--- a/data/trans_dic/P33B_R3-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R3-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,54; 18,04</t>
+          <t>11,59; 17,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,3</t>
+          <t>13,16; 18,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,93</t>
+          <t>13,11; 17,27</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 16,6</t>
+          <t>10,06; 15,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 18,56</t>
+          <t>13,35; 19,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 16,68</t>
+          <t>12,41; 16,78</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,07; 22,07</t>
+          <t>16,33; 23,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 34,16</t>
+          <t>22,83; 34,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 23,49</t>
+          <t>19,44; 25,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 19,13</t>
+          <t>14,63; 19,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 21,05</t>
+          <t>17,95; 22,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,86</t>
+          <t>16,84; 20,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,29; 22,01</t>
+          <t>12,93; 19,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,73; 30,47</t>
+          <t>26,27; 31,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 25,58</t>
+          <t>21,77; 25,78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 12,34</t>
+          <t>2,96; 12,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,08; 25,01</t>
+          <t>20,44; 25,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,35; 20,73</t>
+          <t>16,88; 21,44</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,17</t>
+          <t>14,24; 16,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,3; 21,92</t>
+          <t>21,08; 23,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,87; 18,78</t>
+          <t>18,13; 19,92</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>72088</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>76488</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>140104</t>
+          <t>156040</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>58320; 91162</t>
+          <t>63835; 96561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57707; 81877</t>
+          <t>64296; 90965</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122175; 161315</t>
+          <t>136212; 179466</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>62074</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58997</t>
+          <t>68529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118119</t>
+          <t>130603</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46242; 74925</t>
+          <t>48512; 76266</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48293; 71006</t>
+          <t>56489; 82185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101216; 139105</t>
+          <t>112362; 151939</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>94556</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>53187</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135181</t>
+          <t>147742</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33871; 147499</t>
+          <t>76992; 112158</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38704; 57021</t>
+          <t>42800; 63856</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63269; 196207</t>
+          <t>128112; 168165</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>191019</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>157505</t>
+          <t>176234</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329539</t>
+          <t>367253</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>149382; 197979</t>
+          <t>165635; 218017</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90340; 205858</t>
+          <t>154580; 195621</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>231984; 379659</t>
+          <t>335599; 400093</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>90443</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>218939</t>
+          <t>240800</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302826</t>
+          <t>331242</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67725; 104332</t>
+          <t>73283; 109634</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165515; 255653</t>
+          <t>218040; 261927</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>245739; 335901</t>
+          <t>304094; 360172</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>170735</t>
+          <t>191926</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185157</t>
+          <t>206854</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5731; 29683</t>
+          <t>7014; 30744</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>152895; 190429</t>
+          <t>172581; 212549</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>163830; 207674</t>
+          <t>182566; 231865</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>489578</t>
+          <t>532572</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>721347</t>
+          <t>807163</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1210925</t>
+          <t>1339736</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>390862; 545692</t>
+          <t>489879; 579425</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>582924; 783803</t>
+          <t>766214; 847816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1033101; 1304774</t>
+          <t>1282416; 1409615</t>
         </is>
       </c>
     </row>
